--- a/StructureDefinition-access-data-reporting-composition.xlsx
+++ b/StructureDefinition-access-data-reporting-composition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21839" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21839" uniqueCount="1065">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2109,14 +2109,6 @@
   </si>
   <si>
     <t>Composition.section:eCKM.section:lipids.code</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="57698-3"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Composition.section:eCKM.section:lipids.author</t>
@@ -32064,7 +32056,7 @@
         <v>78</v>
       </c>
       <c r="S241" t="s" s="2">
-        <v>667</v>
+        <v>502</v>
       </c>
       <c r="T241" t="s" s="2">
         <v>78</v>
@@ -32135,7 +32127,7 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>461</v>
@@ -32252,7 +32244,7 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>463</v>
@@ -32369,7 +32361,7 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B244" t="s" s="2">
         <v>465</v>
@@ -32486,7 +32478,7 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B245" t="s" s="2">
         <v>467</v>
@@ -32605,7 +32597,7 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B246" t="s" s="2">
         <v>469</v>
@@ -32724,7 +32716,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B247" t="s" s="2">
         <v>471</v>
@@ -32841,7 +32833,7 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>473</v>
@@ -32960,7 +32952,7 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>475</v>
@@ -33077,7 +33069,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>427</v>
@@ -33196,7 +33188,7 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>451</v>
@@ -33311,7 +33303,7 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>453</v>
@@ -33428,7 +33420,7 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B253" t="s" s="2">
         <v>455</v>
@@ -33547,7 +33539,7 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B254" t="s" s="2">
         <v>457</v>
@@ -33666,7 +33658,7 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>459</v>
@@ -33785,7 +33777,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>461</v>
@@ -33902,7 +33894,7 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B257" t="s" s="2">
         <v>463</v>
@@ -34019,7 +34011,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>465</v>
@@ -34136,7 +34128,7 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B259" t="s" s="2">
         <v>467</v>
@@ -34255,7 +34247,7 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>469</v>
@@ -34374,7 +34366,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>471</v>
@@ -34491,7 +34483,7 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>473</v>
@@ -34610,7 +34602,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>475</v>
@@ -34727,7 +34719,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>427</v>
@@ -34846,7 +34838,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>451</v>
@@ -34961,7 +34953,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>453</v>
@@ -35078,7 +35070,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>455</v>
@@ -35197,7 +35189,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>457</v>
@@ -35316,7 +35308,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>459</v>
@@ -35435,7 +35427,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>461</v>
@@ -35552,7 +35544,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>463</v>
@@ -35669,7 +35661,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>465</v>
@@ -35786,7 +35778,7 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>467</v>
@@ -35905,7 +35897,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>469</v>
@@ -36024,7 +36016,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>471</v>
@@ -36141,7 +36133,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>473</v>
@@ -36260,7 +36252,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>475</v>
@@ -36377,7 +36369,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>427</v>
@@ -36496,7 +36488,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>451</v>
@@ -36611,7 +36603,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>453</v>
@@ -36728,7 +36720,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>455</v>
@@ -36847,7 +36839,7 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>457</v>
@@ -36966,7 +36958,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>459</v>
@@ -37085,7 +37077,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>461</v>
@@ -37202,7 +37194,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>463</v>
@@ -37319,7 +37311,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>465</v>
@@ -37436,7 +37428,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>467</v>
@@ -37555,7 +37547,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>469</v>
@@ -37674,7 +37666,7 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>471</v>
@@ -37791,7 +37783,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>473</v>
@@ -37910,7 +37902,7 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>475</v>
@@ -38027,7 +38019,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>427</v>
@@ -38146,7 +38138,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>451</v>
@@ -38261,7 +38253,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>453</v>
@@ -38378,7 +38370,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>455</v>
@@ -38497,7 +38489,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>457</v>
@@ -38616,7 +38608,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>459</v>
@@ -38735,7 +38727,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>461</v>
@@ -38852,7 +38844,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>463</v>
@@ -38969,7 +38961,7 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B300" t="s" s="2">
         <v>465</v>
@@ -39086,7 +39078,7 @@
     </row>
     <row r="301" hidden="true">
       <c r="A301" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B301" t="s" s="2">
         <v>467</v>
@@ -39205,7 +39197,7 @@
     </row>
     <row r="302" hidden="true">
       <c r="A302" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B302" t="s" s="2">
         <v>469</v>
@@ -39324,7 +39316,7 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B303" t="s" s="2">
         <v>471</v>
@@ -39441,7 +39433,7 @@
     </row>
     <row r="304" hidden="true">
       <c r="A304" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B304" t="s" s="2">
         <v>473</v>
@@ -39560,7 +39552,7 @@
     </row>
     <row r="305" hidden="true">
       <c r="A305" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B305" t="s" s="2">
         <v>475</v>
@@ -39677,13 +39669,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B306" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D306" t="s" s="2">
         <v>78</v>
@@ -39708,7 +39700,7 @@
         <v>252</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M306" t="s" s="2">
         <v>358</v>
@@ -39794,7 +39786,7 @@
     </row>
     <row r="307" hidden="true">
       <c r="A307" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B307" t="s" s="2">
         <v>365</v>
@@ -39909,7 +39901,7 @@
     </row>
     <row r="308" hidden="true">
       <c r="A308" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B308" t="s" s="2">
         <v>366</v>
@@ -40026,7 +40018,7 @@
     </row>
     <row r="309" hidden="true">
       <c r="A309" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B309" t="s" s="2">
         <v>367</v>
@@ -40145,7 +40137,7 @@
     </row>
     <row r="310" hidden="true">
       <c r="A310" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B310" t="s" s="2">
         <v>368</v>
@@ -40264,7 +40256,7 @@
     </row>
     <row r="311" hidden="true">
       <c r="A311" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B311" t="s" s="2">
         <v>374</v>
@@ -40312,7 +40304,7 @@
         <v>78</v>
       </c>
       <c r="S311" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="T311" t="s" s="2">
         <v>78</v>
@@ -40383,7 +40375,7 @@
     </row>
     <row r="312" hidden="true">
       <c r="A312" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B312" t="s" s="2">
         <v>381</v>
@@ -40500,7 +40492,7 @@
     </row>
     <row r="313" hidden="true">
       <c r="A313" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B313" t="s" s="2">
         <v>385</v>
@@ -40617,7 +40609,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B314" t="s" s="2">
         <v>390</v>
@@ -40734,7 +40726,7 @@
     </row>
     <row r="315" hidden="true">
       <c r="A315" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B315" t="s" s="2">
         <v>396</v>
@@ -40853,7 +40845,7 @@
     </row>
     <row r="316" hidden="true">
       <c r="A316" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B316" t="s" s="2">
         <v>404</v>
@@ -40972,7 +40964,7 @@
     </row>
     <row r="317" hidden="true">
       <c r="A317" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B317" t="s" s="2">
         <v>412</v>
@@ -41089,7 +41081,7 @@
     </row>
     <row r="318" hidden="true">
       <c r="A318" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B318" t="s" s="2">
         <v>419</v>
@@ -41208,7 +41200,7 @@
     </row>
     <row r="319" hidden="true">
       <c r="A319" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B319" t="s" s="2">
         <v>427</v>
@@ -41284,7 +41276,7 @@
         <v>359</v>
       </c>
       <c r="AC319" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AD319" t="s" s="2">
         <v>78</v>
@@ -41325,7 +41317,7 @@
     </row>
     <row r="320" hidden="true">
       <c r="A320" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B320" t="s" s="2">
         <v>451</v>
@@ -41440,7 +41432,7 @@
     </row>
     <row r="321" hidden="true">
       <c r="A321" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B321" t="s" s="2">
         <v>453</v>
@@ -41557,7 +41549,7 @@
     </row>
     <row r="322" hidden="true">
       <c r="A322" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B322" t="s" s="2">
         <v>455</v>
@@ -41676,7 +41668,7 @@
     </row>
     <row r="323" hidden="true">
       <c r="A323" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B323" t="s" s="2">
         <v>457</v>
@@ -41795,7 +41787,7 @@
     </row>
     <row r="324" hidden="true">
       <c r="A324" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B324" t="s" s="2">
         <v>459</v>
@@ -41914,7 +41906,7 @@
     </row>
     <row r="325" hidden="true">
       <c r="A325" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B325" t="s" s="2">
         <v>461</v>
@@ -42031,7 +42023,7 @@
     </row>
     <row r="326" hidden="true">
       <c r="A326" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B326" t="s" s="2">
         <v>463</v>
@@ -42148,7 +42140,7 @@
     </row>
     <row r="327" hidden="true">
       <c r="A327" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B327" t="s" s="2">
         <v>465</v>
@@ -42265,7 +42257,7 @@
     </row>
     <row r="328" hidden="true">
       <c r="A328" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B328" t="s" s="2">
         <v>467</v>
@@ -42384,7 +42376,7 @@
     </row>
     <row r="329" hidden="true">
       <c r="A329" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B329" t="s" s="2">
         <v>469</v>
@@ -42503,7 +42495,7 @@
     </row>
     <row r="330" hidden="true">
       <c r="A330" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B330" t="s" s="2">
         <v>471</v>
@@ -42620,7 +42612,7 @@
     </row>
     <row r="331" hidden="true">
       <c r="A331" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B331" t="s" s="2">
         <v>473</v>
@@ -42739,7 +42731,7 @@
     </row>
     <row r="332" hidden="true">
       <c r="A332" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B332" t="s" s="2">
         <v>475</v>
@@ -42856,13 +42848,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B333" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D333" t="s" s="2">
         <v>78</v>
@@ -42887,7 +42879,7 @@
         <v>252</v>
       </c>
       <c r="L333" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="M333" t="s" s="2">
         <v>429</v>
@@ -42975,7 +42967,7 @@
     </row>
     <row r="334" hidden="true">
       <c r="A334" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B334" t="s" s="2">
         <v>451</v>
@@ -43090,7 +43082,7 @@
     </row>
     <row r="335" hidden="true">
       <c r="A335" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B335" t="s" s="2">
         <v>453</v>
@@ -43207,7 +43199,7 @@
     </row>
     <row r="336" hidden="true">
       <c r="A336" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B336" t="s" s="2">
         <v>455</v>
@@ -43326,7 +43318,7 @@
     </row>
     <row r="337" hidden="true">
       <c r="A337" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B337" t="s" s="2">
         <v>457</v>
@@ -43445,7 +43437,7 @@
     </row>
     <row r="338" hidden="true">
       <c r="A338" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B338" t="s" s="2">
         <v>459</v>
@@ -43493,7 +43485,7 @@
         <v>78</v>
       </c>
       <c r="S338" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="T338" t="s" s="2">
         <v>78</v>
@@ -43564,7 +43556,7 @@
     </row>
     <row r="339" hidden="true">
       <c r="A339" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B339" t="s" s="2">
         <v>461</v>
@@ -43681,7 +43673,7 @@
     </row>
     <row r="340" hidden="true">
       <c r="A340" t="s" s="2">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B340" t="s" s="2">
         <v>463</v>
@@ -43798,7 +43790,7 @@
     </row>
     <row r="341" hidden="true">
       <c r="A341" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>465</v>
@@ -43915,7 +43907,7 @@
     </row>
     <row r="342" hidden="true">
       <c r="A342" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>467</v>
@@ -44034,7 +44026,7 @@
     </row>
     <row r="343" hidden="true">
       <c r="A343" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B343" t="s" s="2">
         <v>469</v>
@@ -44153,7 +44145,7 @@
     </row>
     <row r="344">
       <c r="A344" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B344" t="s" s="2">
         <v>471</v>
@@ -44179,7 +44171,7 @@
         <v>78</v>
       </c>
       <c r="K344" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L344" t="s" s="2">
         <v>413</v>
@@ -44270,7 +44262,7 @@
     </row>
     <row r="345" hidden="true">
       <c r="A345" t="s" s="2">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B345" t="s" s="2">
         <v>473</v>
@@ -44389,7 +44381,7 @@
     </row>
     <row r="346" hidden="true">
       <c r="A346" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B346" t="s" s="2">
         <v>475</v>
@@ -44506,13 +44498,13 @@
     </row>
     <row r="347">
       <c r="A347" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B347" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D347" t="s" s="2">
         <v>78</v>
@@ -44537,7 +44529,7 @@
         <v>252</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="M347" t="s" s="2">
         <v>429</v>
@@ -44625,7 +44617,7 @@
     </row>
     <row r="348" hidden="true">
       <c r="A348" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B348" t="s" s="2">
         <v>451</v>
@@ -44740,7 +44732,7 @@
     </row>
     <row r="349" hidden="true">
       <c r="A349" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B349" t="s" s="2">
         <v>453</v>
@@ -44857,7 +44849,7 @@
     </row>
     <row r="350" hidden="true">
       <c r="A350" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B350" t="s" s="2">
         <v>455</v>
@@ -44976,7 +44968,7 @@
     </row>
     <row r="351" hidden="true">
       <c r="A351" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B351" t="s" s="2">
         <v>457</v>
@@ -45095,7 +45087,7 @@
     </row>
     <row r="352" hidden="true">
       <c r="A352" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B352" t="s" s="2">
         <v>459</v>
@@ -45143,7 +45135,7 @@
         <v>78</v>
       </c>
       <c r="S352" t="s" s="2">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T352" t="s" s="2">
         <v>78</v>
@@ -45214,7 +45206,7 @@
     </row>
     <row r="353" hidden="true">
       <c r="A353" t="s" s="2">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B353" t="s" s="2">
         <v>461</v>
@@ -45331,7 +45323,7 @@
     </row>
     <row r="354" hidden="true">
       <c r="A354" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B354" t="s" s="2">
         <v>463</v>
@@ -45448,7 +45440,7 @@
     </row>
     <row r="355" hidden="true">
       <c r="A355" t="s" s="2">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B355" t="s" s="2">
         <v>465</v>
@@ -45565,7 +45557,7 @@
     </row>
     <row r="356" hidden="true">
       <c r="A356" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B356" t="s" s="2">
         <v>467</v>
@@ -45684,7 +45676,7 @@
     </row>
     <row r="357" hidden="true">
       <c r="A357" t="s" s="2">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B357" t="s" s="2">
         <v>469</v>
@@ -45803,7 +45795,7 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B358" t="s" s="2">
         <v>471</v>
@@ -45829,7 +45821,7 @@
         <v>78</v>
       </c>
       <c r="K358" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L358" t="s" s="2">
         <v>413</v>
@@ -45920,7 +45912,7 @@
     </row>
     <row r="359" hidden="true">
       <c r="A359" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B359" t="s" s="2">
         <v>473</v>
@@ -46039,7 +46031,7 @@
     </row>
     <row r="360" hidden="true">
       <c r="A360" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B360" t="s" s="2">
         <v>475</v>
@@ -46156,13 +46148,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B361" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D361" t="s" s="2">
         <v>78</v>
@@ -46187,7 +46179,7 @@
         <v>252</v>
       </c>
       <c r="L361" t="s" s="2">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="M361" t="s" s="2">
         <v>429</v>
@@ -46275,7 +46267,7 @@
     </row>
     <row r="362" hidden="true">
       <c r="A362" t="s" s="2">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B362" t="s" s="2">
         <v>451</v>
@@ -46390,7 +46382,7 @@
     </row>
     <row r="363" hidden="true">
       <c r="A363" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B363" t="s" s="2">
         <v>453</v>
@@ -46507,7 +46499,7 @@
     </row>
     <row r="364" hidden="true">
       <c r="A364" t="s" s="2">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B364" t="s" s="2">
         <v>455</v>
@@ -46626,7 +46618,7 @@
     </row>
     <row r="365" hidden="true">
       <c r="A365" t="s" s="2">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B365" t="s" s="2">
         <v>457</v>
@@ -46745,7 +46737,7 @@
     </row>
     <row r="366" hidden="true">
       <c r="A366" t="s" s="2">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B366" t="s" s="2">
         <v>459</v>
@@ -46793,7 +46785,7 @@
         <v>78</v>
       </c>
       <c r="S366" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="T366" t="s" s="2">
         <v>78</v>
@@ -46864,7 +46856,7 @@
     </row>
     <row r="367" hidden="true">
       <c r="A367" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B367" t="s" s="2">
         <v>461</v>
@@ -46981,7 +46973,7 @@
     </row>
     <row r="368" hidden="true">
       <c r="A368" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>463</v>
@@ -47098,7 +47090,7 @@
     </row>
     <row r="369" hidden="true">
       <c r="A369" t="s" s="2">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>465</v>
@@ -47215,7 +47207,7 @@
     </row>
     <row r="370" hidden="true">
       <c r="A370" t="s" s="2">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>467</v>
@@ -47334,7 +47326,7 @@
     </row>
     <row r="371" hidden="true">
       <c r="A371" t="s" s="2">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>469</v>
@@ -47453,7 +47445,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>471</v>
@@ -47479,7 +47471,7 @@
         <v>78</v>
       </c>
       <c r="K372" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L372" t="s" s="2">
         <v>413</v>
@@ -47570,7 +47562,7 @@
     </row>
     <row r="373" hidden="true">
       <c r="A373" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>473</v>
@@ -47689,7 +47681,7 @@
     </row>
     <row r="374" hidden="true">
       <c r="A374" t="s" s="2">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>475</v>
@@ -47806,13 +47798,13 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D375" t="s" s="2">
         <v>78</v>
@@ -47837,7 +47829,7 @@
         <v>252</v>
       </c>
       <c r="L375" t="s" s="2">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="M375" t="s" s="2">
         <v>429</v>
@@ -47925,7 +47917,7 @@
     </row>
     <row r="376" hidden="true">
       <c r="A376" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>451</v>
@@ -48040,7 +48032,7 @@
     </row>
     <row r="377" hidden="true">
       <c r="A377" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>453</v>
@@ -48157,7 +48149,7 @@
     </row>
     <row r="378" hidden="true">
       <c r="A378" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>455</v>
@@ -48276,7 +48268,7 @@
     </row>
     <row r="379" hidden="true">
       <c r="A379" t="s" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>457</v>
@@ -48395,7 +48387,7 @@
     </row>
     <row r="380" hidden="true">
       <c r="A380" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>459</v>
@@ -48443,7 +48435,7 @@
         <v>78</v>
       </c>
       <c r="S380" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="T380" t="s" s="2">
         <v>78</v>
@@ -48514,7 +48506,7 @@
     </row>
     <row r="381" hidden="true">
       <c r="A381" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>461</v>
@@ -48631,7 +48623,7 @@
     </row>
     <row r="382" hidden="true">
       <c r="A382" t="s" s="2">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>463</v>
@@ -48748,7 +48740,7 @@
     </row>
     <row r="383" hidden="true">
       <c r="A383" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>465</v>
@@ -48865,7 +48857,7 @@
     </row>
     <row r="384" hidden="true">
       <c r="A384" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>467</v>
@@ -48984,7 +48976,7 @@
     </row>
     <row r="385" hidden="true">
       <c r="A385" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>469</v>
@@ -49103,7 +49095,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>471</v>
@@ -49129,7 +49121,7 @@
         <v>78</v>
       </c>
       <c r="K386" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L386" t="s" s="2">
         <v>413</v>
@@ -49220,7 +49212,7 @@
     </row>
     <row r="387" hidden="true">
       <c r="A387" t="s" s="2">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>473</v>
@@ -49339,7 +49331,7 @@
     </row>
     <row r="388" hidden="true">
       <c r="A388" t="s" s="2">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>475</v>
@@ -49456,13 +49448,13 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D389" t="s" s="2">
         <v>78</v>
@@ -49487,7 +49479,7 @@
         <v>252</v>
       </c>
       <c r="L389" t="s" s="2">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="M389" t="s" s="2">
         <v>429</v>
@@ -49575,7 +49567,7 @@
     </row>
     <row r="390" hidden="true">
       <c r="A390" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>451</v>
@@ -49690,7 +49682,7 @@
     </row>
     <row r="391" hidden="true">
       <c r="A391" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>453</v>
@@ -49807,7 +49799,7 @@
     </row>
     <row r="392" hidden="true">
       <c r="A392" t="s" s="2">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>455</v>
@@ -49926,7 +49918,7 @@
     </row>
     <row r="393" hidden="true">
       <c r="A393" t="s" s="2">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>457</v>
@@ -50045,7 +50037,7 @@
     </row>
     <row r="394" hidden="true">
       <c r="A394" t="s" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>459</v>
@@ -50093,7 +50085,7 @@
         <v>78</v>
       </c>
       <c r="S394" t="s" s="2">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="T394" t="s" s="2">
         <v>78</v>
@@ -50164,7 +50156,7 @@
     </row>
     <row r="395" hidden="true">
       <c r="A395" t="s" s="2">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>461</v>
@@ -50281,7 +50273,7 @@
     </row>
     <row r="396" hidden="true">
       <c r="A396" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>463</v>
@@ -50398,7 +50390,7 @@
     </row>
     <row r="397" hidden="true">
       <c r="A397" t="s" s="2">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>465</v>
@@ -50515,7 +50507,7 @@
     </row>
     <row r="398" hidden="true">
       <c r="A398" t="s" s="2">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>467</v>
@@ -50634,7 +50626,7 @@
     </row>
     <row r="399" hidden="true">
       <c r="A399" t="s" s="2">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>469</v>
@@ -50753,7 +50745,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>471</v>
@@ -50779,7 +50771,7 @@
         <v>78</v>
       </c>
       <c r="K400" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L400" t="s" s="2">
         <v>413</v>
@@ -50870,7 +50862,7 @@
     </row>
     <row r="401" hidden="true">
       <c r="A401" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>473</v>
@@ -50989,7 +50981,7 @@
     </row>
     <row r="402" hidden="true">
       <c r="A402" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>475</v>
@@ -51106,13 +51098,13 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="D403" t="s" s="2">
         <v>78</v>
@@ -51137,7 +51129,7 @@
         <v>252</v>
       </c>
       <c r="L403" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="M403" t="s" s="2">
         <v>429</v>
@@ -51225,7 +51217,7 @@
     </row>
     <row r="404" hidden="true">
       <c r="A404" t="s" s="2">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>451</v>
@@ -51340,7 +51332,7 @@
     </row>
     <row r="405" hidden="true">
       <c r="A405" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>453</v>
@@ -51457,7 +51449,7 @@
     </row>
     <row r="406" hidden="true">
       <c r="A406" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>455</v>
@@ -51576,7 +51568,7 @@
     </row>
     <row r="407" hidden="true">
       <c r="A407" t="s" s="2">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>457</v>
@@ -51695,7 +51687,7 @@
     </row>
     <row r="408" hidden="true">
       <c r="A408" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>459</v>
@@ -51743,7 +51735,7 @@
         <v>78</v>
       </c>
       <c r="S408" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="T408" t="s" s="2">
         <v>78</v>
@@ -51814,7 +51806,7 @@
     </row>
     <row r="409" hidden="true">
       <c r="A409" t="s" s="2">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>461</v>
@@ -51931,7 +51923,7 @@
     </row>
     <row r="410" hidden="true">
       <c r="A410" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>463</v>
@@ -52048,7 +52040,7 @@
     </row>
     <row r="411" hidden="true">
       <c r="A411" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>465</v>
@@ -52165,7 +52157,7 @@
     </row>
     <row r="412" hidden="true">
       <c r="A412" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>467</v>
@@ -52284,7 +52276,7 @@
     </row>
     <row r="413" hidden="true">
       <c r="A413" t="s" s="2">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>469</v>
@@ -52403,7 +52395,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>471</v>
@@ -52429,7 +52421,7 @@
         <v>78</v>
       </c>
       <c r="K414" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L414" t="s" s="2">
         <v>413</v>
@@ -52520,7 +52512,7 @@
     </row>
     <row r="415" hidden="true">
       <c r="A415" t="s" s="2">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>473</v>
@@ -52639,7 +52631,7 @@
     </row>
     <row r="416" hidden="true">
       <c r="A416" t="s" s="2">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>475</v>
@@ -52756,13 +52748,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D417" t="s" s="2">
         <v>78</v>
@@ -52787,7 +52779,7 @@
         <v>252</v>
       </c>
       <c r="L417" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M417" t="s" s="2">
         <v>429</v>
@@ -52875,7 +52867,7 @@
     </row>
     <row r="418" hidden="true">
       <c r="A418" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>451</v>
@@ -52990,7 +52982,7 @@
     </row>
     <row r="419" hidden="true">
       <c r="A419" t="s" s="2">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>453</v>
@@ -53107,7 +53099,7 @@
     </row>
     <row r="420" hidden="true">
       <c r="A420" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>455</v>
@@ -53226,7 +53218,7 @@
     </row>
     <row r="421" hidden="true">
       <c r="A421" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>457</v>
@@ -53345,7 +53337,7 @@
     </row>
     <row r="422" hidden="true">
       <c r="A422" t="s" s="2">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>459</v>
@@ -53393,7 +53385,7 @@
         <v>78</v>
       </c>
       <c r="S422" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="T422" t="s" s="2">
         <v>78</v>
@@ -53464,7 +53456,7 @@
     </row>
     <row r="423" hidden="true">
       <c r="A423" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>461</v>
@@ -53581,7 +53573,7 @@
     </row>
     <row r="424" hidden="true">
       <c r="A424" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>463</v>
@@ -53698,7 +53690,7 @@
     </row>
     <row r="425" hidden="true">
       <c r="A425" t="s" s="2">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>465</v>
@@ -53815,7 +53807,7 @@
     </row>
     <row r="426" hidden="true">
       <c r="A426" t="s" s="2">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>467</v>
@@ -53934,7 +53926,7 @@
     </row>
     <row r="427" hidden="true">
       <c r="A427" t="s" s="2">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>469</v>
@@ -54053,7 +54045,7 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B428" t="s" s="2">
         <v>471</v>
@@ -54079,7 +54071,7 @@
         <v>78</v>
       </c>
       <c r="K428" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L428" t="s" s="2">
         <v>413</v>
@@ -54170,7 +54162,7 @@
     </row>
     <row r="429" hidden="true">
       <c r="A429" t="s" s="2">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B429" t="s" s="2">
         <v>473</v>
@@ -54289,7 +54281,7 @@
     </row>
     <row r="430" hidden="true">
       <c r="A430" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B430" t="s" s="2">
         <v>475</v>
@@ -54406,13 +54398,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B431" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D431" t="s" s="2">
         <v>78</v>
@@ -54437,7 +54429,7 @@
         <v>252</v>
       </c>
       <c r="L431" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="M431" t="s" s="2">
         <v>429</v>
@@ -54525,7 +54517,7 @@
     </row>
     <row r="432" hidden="true">
       <c r="A432" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B432" t="s" s="2">
         <v>451</v>
@@ -54640,7 +54632,7 @@
     </row>
     <row r="433" hidden="true">
       <c r="A433" t="s" s="2">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B433" t="s" s="2">
         <v>453</v>
@@ -54757,7 +54749,7 @@
     </row>
     <row r="434" hidden="true">
       <c r="A434" t="s" s="2">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B434" t="s" s="2">
         <v>455</v>
@@ -54876,7 +54868,7 @@
     </row>
     <row r="435" hidden="true">
       <c r="A435" t="s" s="2">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B435" t="s" s="2">
         <v>457</v>
@@ -54995,7 +54987,7 @@
     </row>
     <row r="436" hidden="true">
       <c r="A436" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B436" t="s" s="2">
         <v>459</v>
@@ -55043,7 +55035,7 @@
         <v>78</v>
       </c>
       <c r="S436" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="T436" t="s" s="2">
         <v>78</v>
@@ -55114,7 +55106,7 @@
     </row>
     <row r="437" hidden="true">
       <c r="A437" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B437" t="s" s="2">
         <v>461</v>
@@ -55231,7 +55223,7 @@
     </row>
     <row r="438" hidden="true">
       <c r="A438" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B438" t="s" s="2">
         <v>463</v>
@@ -55348,7 +55340,7 @@
     </row>
     <row r="439" hidden="true">
       <c r="A439" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B439" t="s" s="2">
         <v>465</v>
@@ -55465,7 +55457,7 @@
     </row>
     <row r="440" hidden="true">
       <c r="A440" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B440" t="s" s="2">
         <v>467</v>
@@ -55584,7 +55576,7 @@
     </row>
     <row r="441" hidden="true">
       <c r="A441" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B441" t="s" s="2">
         <v>469</v>
@@ -55703,7 +55695,7 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B442" t="s" s="2">
         <v>471</v>
@@ -55729,7 +55721,7 @@
         <v>78</v>
       </c>
       <c r="K442" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L442" t="s" s="2">
         <v>413</v>
@@ -55820,7 +55812,7 @@
     </row>
     <row r="443" hidden="true">
       <c r="A443" t="s" s="2">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B443" t="s" s="2">
         <v>473</v>
@@ -55939,7 +55931,7 @@
     </row>
     <row r="444" hidden="true">
       <c r="A444" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B444" t="s" s="2">
         <v>475</v>
@@ -56056,13 +56048,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B445" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D445" t="s" s="2">
         <v>78</v>
@@ -56087,7 +56079,7 @@
         <v>252</v>
       </c>
       <c r="L445" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="M445" t="s" s="2">
         <v>429</v>
@@ -56175,7 +56167,7 @@
     </row>
     <row r="446" hidden="true">
       <c r="A446" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B446" t="s" s="2">
         <v>451</v>
@@ -56290,7 +56282,7 @@
     </row>
     <row r="447" hidden="true">
       <c r="A447" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B447" t="s" s="2">
         <v>453</v>
@@ -56407,7 +56399,7 @@
     </row>
     <row r="448" hidden="true">
       <c r="A448" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B448" t="s" s="2">
         <v>455</v>
@@ -56526,7 +56518,7 @@
     </row>
     <row r="449" hidden="true">
       <c r="A449" t="s" s="2">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B449" t="s" s="2">
         <v>457</v>
@@ -56645,7 +56637,7 @@
     </row>
     <row r="450" hidden="true">
       <c r="A450" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B450" t="s" s="2">
         <v>459</v>
@@ -56693,7 +56685,7 @@
         <v>78</v>
       </c>
       <c r="S450" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="T450" t="s" s="2">
         <v>78</v>
@@ -56764,7 +56756,7 @@
     </row>
     <row r="451" hidden="true">
       <c r="A451" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B451" t="s" s="2">
         <v>461</v>
@@ -56881,7 +56873,7 @@
     </row>
     <row r="452" hidden="true">
       <c r="A452" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B452" t="s" s="2">
         <v>463</v>
@@ -56998,7 +56990,7 @@
     </row>
     <row r="453" hidden="true">
       <c r="A453" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B453" t="s" s="2">
         <v>465</v>
@@ -57115,7 +57107,7 @@
     </row>
     <row r="454" hidden="true">
       <c r="A454" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B454" t="s" s="2">
         <v>467</v>
@@ -57234,7 +57226,7 @@
     </row>
     <row r="455" hidden="true">
       <c r="A455" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B455" t="s" s="2">
         <v>469</v>
@@ -57353,7 +57345,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B456" t="s" s="2">
         <v>471</v>
@@ -57379,7 +57371,7 @@
         <v>78</v>
       </c>
       <c r="K456" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L456" t="s" s="2">
         <v>413</v>
@@ -57470,7 +57462,7 @@
     </row>
     <row r="457" hidden="true">
       <c r="A457" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B457" t="s" s="2">
         <v>473</v>
@@ -57589,7 +57581,7 @@
     </row>
     <row r="458" hidden="true">
       <c r="A458" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B458" t="s" s="2">
         <v>475</v>
@@ -57706,13 +57698,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B459" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D459" t="s" s="2">
         <v>78</v>
@@ -57737,7 +57729,7 @@
         <v>252</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="M459" t="s" s="2">
         <v>429</v>
@@ -57825,7 +57817,7 @@
     </row>
     <row r="460" hidden="true">
       <c r="A460" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B460" t="s" s="2">
         <v>451</v>
@@ -57940,7 +57932,7 @@
     </row>
     <row r="461" hidden="true">
       <c r="A461" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B461" t="s" s="2">
         <v>453</v>
@@ -58057,7 +58049,7 @@
     </row>
     <row r="462" hidden="true">
       <c r="A462" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B462" t="s" s="2">
         <v>455</v>
@@ -58176,7 +58168,7 @@
     </row>
     <row r="463" hidden="true">
       <c r="A463" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B463" t="s" s="2">
         <v>457</v>
@@ -58295,7 +58287,7 @@
     </row>
     <row r="464" hidden="true">
       <c r="A464" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B464" t="s" s="2">
         <v>459</v>
@@ -58343,7 +58335,7 @@
         <v>78</v>
       </c>
       <c r="S464" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="T464" t="s" s="2">
         <v>78</v>
@@ -58414,7 +58406,7 @@
     </row>
     <row r="465" hidden="true">
       <c r="A465" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B465" t="s" s="2">
         <v>461</v>
@@ -58531,7 +58523,7 @@
     </row>
     <row r="466" hidden="true">
       <c r="A466" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B466" t="s" s="2">
         <v>463</v>
@@ -58648,7 +58640,7 @@
     </row>
     <row r="467" hidden="true">
       <c r="A467" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B467" t="s" s="2">
         <v>465</v>
@@ -58765,7 +58757,7 @@
     </row>
     <row r="468" hidden="true">
       <c r="A468" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B468" t="s" s="2">
         <v>467</v>
@@ -58884,7 +58876,7 @@
     </row>
     <row r="469" hidden="true">
       <c r="A469" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B469" t="s" s="2">
         <v>469</v>
@@ -59003,7 +58995,7 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B470" t="s" s="2">
         <v>471</v>
@@ -59029,7 +59021,7 @@
         <v>78</v>
       </c>
       <c r="K470" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L470" t="s" s="2">
         <v>413</v>
@@ -59120,7 +59112,7 @@
     </row>
     <row r="471" hidden="true">
       <c r="A471" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B471" t="s" s="2">
         <v>473</v>
@@ -59239,7 +59231,7 @@
     </row>
     <row r="472" hidden="true">
       <c r="A472" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B472" t="s" s="2">
         <v>475</v>
@@ -59356,13 +59348,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B473" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D473" t="s" s="2">
         <v>78</v>
@@ -59387,7 +59379,7 @@
         <v>252</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M473" t="s" s="2">
         <v>429</v>
@@ -59475,7 +59467,7 @@
     </row>
     <row r="474" hidden="true">
       <c r="A474" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B474" t="s" s="2">
         <v>451</v>
@@ -59590,7 +59582,7 @@
     </row>
     <row r="475" hidden="true">
       <c r="A475" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B475" t="s" s="2">
         <v>453</v>
@@ -59707,7 +59699,7 @@
     </row>
     <row r="476" hidden="true">
       <c r="A476" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B476" t="s" s="2">
         <v>455</v>
@@ -59826,7 +59818,7 @@
     </row>
     <row r="477" hidden="true">
       <c r="A477" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B477" t="s" s="2">
         <v>457</v>
@@ -59945,7 +59937,7 @@
     </row>
     <row r="478" hidden="true">
       <c r="A478" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B478" t="s" s="2">
         <v>459</v>
@@ -59993,7 +59985,7 @@
         <v>78</v>
       </c>
       <c r="S478" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="T478" t="s" s="2">
         <v>78</v>
@@ -60064,7 +60056,7 @@
     </row>
     <row r="479" hidden="true">
       <c r="A479" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B479" t="s" s="2">
         <v>461</v>
@@ -60181,7 +60173,7 @@
     </row>
     <row r="480" hidden="true">
       <c r="A480" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B480" t="s" s="2">
         <v>463</v>
@@ -60298,7 +60290,7 @@
     </row>
     <row r="481" hidden="true">
       <c r="A481" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B481" t="s" s="2">
         <v>465</v>
@@ -60415,7 +60407,7 @@
     </row>
     <row r="482" hidden="true">
       <c r="A482" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B482" t="s" s="2">
         <v>467</v>
@@ -60534,7 +60526,7 @@
     </row>
     <row r="483" hidden="true">
       <c r="A483" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B483" t="s" s="2">
         <v>469</v>
@@ -60653,7 +60645,7 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B484" t="s" s="2">
         <v>471</v>
@@ -60679,7 +60671,7 @@
         <v>78</v>
       </c>
       <c r="K484" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L484" t="s" s="2">
         <v>413</v>
@@ -60770,7 +60762,7 @@
     </row>
     <row r="485" hidden="true">
       <c r="A485" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B485" t="s" s="2">
         <v>473</v>
@@ -60889,7 +60881,7 @@
     </row>
     <row r="486" hidden="true">
       <c r="A486" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B486" t="s" s="2">
         <v>475</v>
@@ -61006,13 +60998,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B487" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D487" t="s" s="2">
         <v>78</v>
@@ -61037,7 +61029,7 @@
         <v>252</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="M487" t="s" s="2">
         <v>358</v>
@@ -61123,7 +61115,7 @@
     </row>
     <row r="488" hidden="true">
       <c r="A488" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B488" t="s" s="2">
         <v>365</v>
@@ -61238,7 +61230,7 @@
     </row>
     <row r="489" hidden="true">
       <c r="A489" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B489" t="s" s="2">
         <v>366</v>
@@ -61355,7 +61347,7 @@
     </row>
     <row r="490" hidden="true">
       <c r="A490" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B490" t="s" s="2">
         <v>367</v>
@@ -61474,7 +61466,7 @@
     </row>
     <row r="491" hidden="true">
       <c r="A491" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B491" t="s" s="2">
         <v>368</v>
@@ -61593,7 +61585,7 @@
     </row>
     <row r="492" hidden="true">
       <c r="A492" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B492" t="s" s="2">
         <v>374</v>
@@ -61641,7 +61633,7 @@
         <v>78</v>
       </c>
       <c r="S492" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="T492" t="s" s="2">
         <v>78</v>
@@ -61712,7 +61704,7 @@
     </row>
     <row r="493" hidden="true">
       <c r="A493" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B493" t="s" s="2">
         <v>381</v>
@@ -61829,7 +61821,7 @@
     </row>
     <row r="494" hidden="true">
       <c r="A494" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B494" t="s" s="2">
         <v>385</v>
@@ -61946,7 +61938,7 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B495" t="s" s="2">
         <v>390</v>
@@ -62063,7 +62055,7 @@
     </row>
     <row r="496" hidden="true">
       <c r="A496" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B496" t="s" s="2">
         <v>396</v>
@@ -62182,7 +62174,7 @@
     </row>
     <row r="497" hidden="true">
       <c r="A497" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B497" t="s" s="2">
         <v>404</v>
@@ -62301,7 +62293,7 @@
     </row>
     <row r="498" hidden="true">
       <c r="A498" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B498" t="s" s="2">
         <v>412</v>
@@ -62418,7 +62410,7 @@
     </row>
     <row r="499" hidden="true">
       <c r="A499" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B499" t="s" s="2">
         <v>419</v>
@@ -62537,7 +62529,7 @@
     </row>
     <row r="500" hidden="true">
       <c r="A500" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B500" t="s" s="2">
         <v>427</v>
@@ -62613,7 +62605,7 @@
         <v>359</v>
       </c>
       <c r="AC500" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="AD500" t="s" s="2">
         <v>78</v>
@@ -62654,7 +62646,7 @@
     </row>
     <row r="501" hidden="true">
       <c r="A501" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B501" t="s" s="2">
         <v>451</v>
@@ -62769,7 +62761,7 @@
     </row>
     <row r="502" hidden="true">
       <c r="A502" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B502" t="s" s="2">
         <v>453</v>
@@ -62886,7 +62878,7 @@
     </row>
     <row r="503" hidden="true">
       <c r="A503" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B503" t="s" s="2">
         <v>455</v>
@@ -63005,7 +62997,7 @@
     </row>
     <row r="504" hidden="true">
       <c r="A504" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B504" t="s" s="2">
         <v>457</v>
@@ -63124,7 +63116,7 @@
     </row>
     <row r="505" hidden="true">
       <c r="A505" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B505" t="s" s="2">
         <v>459</v>
@@ -63243,7 +63235,7 @@
     </row>
     <row r="506" hidden="true">
       <c r="A506" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B506" t="s" s="2">
         <v>461</v>
@@ -63360,7 +63352,7 @@
     </row>
     <row r="507" hidden="true">
       <c r="A507" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B507" t="s" s="2">
         <v>463</v>
@@ -63477,7 +63469,7 @@
     </row>
     <row r="508" hidden="true">
       <c r="A508" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B508" t="s" s="2">
         <v>465</v>
@@ -63594,7 +63586,7 @@
     </row>
     <row r="509" hidden="true">
       <c r="A509" t="s" s="2">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B509" t="s" s="2">
         <v>467</v>
@@ -63713,7 +63705,7 @@
     </row>
     <row r="510" hidden="true">
       <c r="A510" t="s" s="2">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B510" t="s" s="2">
         <v>469</v>
@@ -63832,7 +63824,7 @@
     </row>
     <row r="511" hidden="true">
       <c r="A511" t="s" s="2">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B511" t="s" s="2">
         <v>471</v>
@@ -63949,7 +63941,7 @@
     </row>
     <row r="512" hidden="true">
       <c r="A512" t="s" s="2">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B512" t="s" s="2">
         <v>473</v>
@@ -64068,7 +64060,7 @@
     </row>
     <row r="513" hidden="true">
       <c r="A513" t="s" s="2">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B513" t="s" s="2">
         <v>475</v>
@@ -64185,13 +64177,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B514" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D514" t="s" s="2">
         <v>78</v>
@@ -64216,7 +64208,7 @@
         <v>252</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="M514" t="s" s="2">
         <v>429</v>
@@ -64304,7 +64296,7 @@
     </row>
     <row r="515" hidden="true">
       <c r="A515" t="s" s="2">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B515" t="s" s="2">
         <v>451</v>
@@ -64419,7 +64411,7 @@
     </row>
     <row r="516" hidden="true">
       <c r="A516" t="s" s="2">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B516" t="s" s="2">
         <v>453</v>
@@ -64536,7 +64528,7 @@
     </row>
     <row r="517" hidden="true">
       <c r="A517" t="s" s="2">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B517" t="s" s="2">
         <v>455</v>
@@ -64655,7 +64647,7 @@
     </row>
     <row r="518" hidden="true">
       <c r="A518" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B518" t="s" s="2">
         <v>457</v>
@@ -64774,7 +64766,7 @@
     </row>
     <row r="519" hidden="true">
       <c r="A519" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B519" t="s" s="2">
         <v>459</v>
@@ -64822,7 +64814,7 @@
         <v>78</v>
       </c>
       <c r="S519" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="T519" t="s" s="2">
         <v>78</v>
@@ -64893,7 +64885,7 @@
     </row>
     <row r="520" hidden="true">
       <c r="A520" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>461</v>
@@ -65010,7 +65002,7 @@
     </row>
     <row r="521" hidden="true">
       <c r="A521" t="s" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B521" t="s" s="2">
         <v>463</v>
@@ -65127,7 +65119,7 @@
     </row>
     <row r="522" hidden="true">
       <c r="A522" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B522" t="s" s="2">
         <v>465</v>
@@ -65244,7 +65236,7 @@
     </row>
     <row r="523" hidden="true">
       <c r="A523" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>467</v>
@@ -65363,7 +65355,7 @@
     </row>
     <row r="524" hidden="true">
       <c r="A524" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B524" t="s" s="2">
         <v>469</v>
@@ -65482,7 +65474,7 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B525" t="s" s="2">
         <v>471</v>
@@ -65508,7 +65500,7 @@
         <v>78</v>
       </c>
       <c r="K525" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L525" t="s" s="2">
         <v>413</v>
@@ -65599,7 +65591,7 @@
     </row>
     <row r="526" hidden="true">
       <c r="A526" t="s" s="2">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B526" t="s" s="2">
         <v>473</v>
@@ -65718,7 +65710,7 @@
     </row>
     <row r="527" hidden="true">
       <c r="A527" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B527" t="s" s="2">
         <v>475</v>
@@ -65835,13 +65827,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B528" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="D528" t="s" s="2">
         <v>78</v>
@@ -65866,7 +65858,7 @@
         <v>252</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="M528" t="s" s="2">
         <v>429</v>
@@ -65954,7 +65946,7 @@
     </row>
     <row r="529" hidden="true">
       <c r="A529" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B529" t="s" s="2">
         <v>451</v>
@@ -66069,7 +66061,7 @@
     </row>
     <row r="530" hidden="true">
       <c r="A530" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B530" t="s" s="2">
         <v>453</v>
@@ -66186,7 +66178,7 @@
     </row>
     <row r="531" hidden="true">
       <c r="A531" t="s" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B531" t="s" s="2">
         <v>455</v>
@@ -66305,7 +66297,7 @@
     </row>
     <row r="532" hidden="true">
       <c r="A532" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B532" t="s" s="2">
         <v>457</v>
@@ -66424,7 +66416,7 @@
     </row>
     <row r="533" hidden="true">
       <c r="A533" t="s" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B533" t="s" s="2">
         <v>459</v>
@@ -66472,7 +66464,7 @@
         <v>78</v>
       </c>
       <c r="S533" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="T533" t="s" s="2">
         <v>78</v>
@@ -66543,7 +66535,7 @@
     </row>
     <row r="534" hidden="true">
       <c r="A534" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B534" t="s" s="2">
         <v>461</v>
@@ -66660,7 +66652,7 @@
     </row>
     <row r="535" hidden="true">
       <c r="A535" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>463</v>
@@ -66777,7 +66769,7 @@
     </row>
     <row r="536" hidden="true">
       <c r="A536" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B536" t="s" s="2">
         <v>465</v>
@@ -66894,7 +66886,7 @@
     </row>
     <row r="537" hidden="true">
       <c r="A537" t="s" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B537" t="s" s="2">
         <v>467</v>
@@ -67013,7 +67005,7 @@
     </row>
     <row r="538" hidden="true">
       <c r="A538" t="s" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B538" t="s" s="2">
         <v>469</v>
@@ -67132,7 +67124,7 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B539" t="s" s="2">
         <v>471</v>
@@ -67158,7 +67150,7 @@
         <v>78</v>
       </c>
       <c r="K539" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L539" t="s" s="2">
         <v>413</v>
@@ -67249,7 +67241,7 @@
     </row>
     <row r="540" hidden="true">
       <c r="A540" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>473</v>
@@ -67368,7 +67360,7 @@
     </row>
     <row r="541" hidden="true">
       <c r="A541" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B541" t="s" s="2">
         <v>475</v>
@@ -67485,13 +67477,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B542" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D542" t="s" s="2">
         <v>78</v>
@@ -67516,7 +67508,7 @@
         <v>252</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="M542" t="s" s="2">
         <v>429</v>
@@ -67604,7 +67596,7 @@
     </row>
     <row r="543" hidden="true">
       <c r="A543" t="s" s="2">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B543" t="s" s="2">
         <v>451</v>
@@ -67719,7 +67711,7 @@
     </row>
     <row r="544" hidden="true">
       <c r="A544" t="s" s="2">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B544" t="s" s="2">
         <v>453</v>
@@ -67836,7 +67828,7 @@
     </row>
     <row r="545" hidden="true">
       <c r="A545" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B545" t="s" s="2">
         <v>455</v>
@@ -67955,7 +67947,7 @@
     </row>
     <row r="546" hidden="true">
       <c r="A546" t="s" s="2">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B546" t="s" s="2">
         <v>457</v>
@@ -68074,7 +68066,7 @@
     </row>
     <row r="547" hidden="true">
       <c r="A547" t="s" s="2">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B547" t="s" s="2">
         <v>459</v>
@@ -68122,7 +68114,7 @@
         <v>78</v>
       </c>
       <c r="S547" t="s" s="2">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="T547" t="s" s="2">
         <v>78</v>
@@ -68193,7 +68185,7 @@
     </row>
     <row r="548" hidden="true">
       <c r="A548" t="s" s="2">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B548" t="s" s="2">
         <v>461</v>
@@ -68310,7 +68302,7 @@
     </row>
     <row r="549" hidden="true">
       <c r="A549" t="s" s="2">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>463</v>
@@ -68427,7 +68419,7 @@
     </row>
     <row r="550" hidden="true">
       <c r="A550" t="s" s="2">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B550" t="s" s="2">
         <v>465</v>
@@ -68544,7 +68536,7 @@
     </row>
     <row r="551" hidden="true">
       <c r="A551" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>467</v>
@@ -68663,7 +68655,7 @@
     </row>
     <row r="552" hidden="true">
       <c r="A552" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B552" t="s" s="2">
         <v>469</v>
@@ -68782,7 +68774,7 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>471</v>
@@ -68808,7 +68800,7 @@
         <v>78</v>
       </c>
       <c r="K553" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L553" t="s" s="2">
         <v>413</v>
@@ -68899,7 +68891,7 @@
     </row>
     <row r="554" hidden="true">
       <c r="A554" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B554" t="s" s="2">
         <v>473</v>
@@ -69018,7 +69010,7 @@
     </row>
     <row r="555" hidden="true">
       <c r="A555" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B555" t="s" s="2">
         <v>475</v>
@@ -69135,13 +69127,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B556" t="s" s="2">
         <v>427</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D556" t="s" s="2">
         <v>78</v>
@@ -69166,7 +69158,7 @@
         <v>252</v>
       </c>
       <c r="L556" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="M556" t="s" s="2">
         <v>429</v>
@@ -69254,7 +69246,7 @@
     </row>
     <row r="557" hidden="true">
       <c r="A557" t="s" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B557" t="s" s="2">
         <v>451</v>
@@ -69369,7 +69361,7 @@
     </row>
     <row r="558" hidden="true">
       <c r="A558" t="s" s="2">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B558" t="s" s="2">
         <v>453</v>
@@ -69486,7 +69478,7 @@
     </row>
     <row r="559" hidden="true">
       <c r="A559" t="s" s="2">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>455</v>
@@ -69605,7 +69597,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>457</v>
@@ -69724,7 +69716,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>459</v>
@@ -69772,7 +69764,7 @@
         <v>78</v>
       </c>
       <c r="S561" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="T561" t="s" s="2">
         <v>78</v>
@@ -69843,7 +69835,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>461</v>
@@ -69960,7 +69952,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>463</v>
@@ -70077,7 +70069,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>465</v>
@@ -70194,7 +70186,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>467</v>
@@ -70313,7 +70305,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>469</v>
@@ -70432,7 +70424,7 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>471</v>
@@ -70458,7 +70450,7 @@
         <v>78</v>
       </c>
       <c r="K567" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L567" t="s" s="2">
         <v>413</v>
@@ -70549,7 +70541,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>473</v>
@@ -70668,7 +70660,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>475</v>
@@ -70785,13 +70777,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>356</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D570" t="s" s="2">
         <v>78</v>
@@ -70816,10 +70808,10 @@
         <v>252</v>
       </c>
       <c r="L570" t="s" s="2">
+        <v>1047</v>
+      </c>
+      <c r="M570" t="s" s="2">
         <v>1048</v>
-      </c>
-      <c r="M570" t="s" s="2">
-        <v>1049</v>
       </c>
       <c r="N570" s="2"/>
       <c r="O570" s="2"/>
@@ -70902,7 +70894,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>365</v>
@@ -71017,7 +71009,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>366</v>
@@ -71134,7 +71126,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>367</v>
@@ -71253,7 +71245,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>368</v>
@@ -71372,7 +71364,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>374</v>
@@ -71420,7 +71412,7 @@
         <v>78</v>
       </c>
       <c r="S575" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="T575" t="s" s="2">
         <v>78</v>
@@ -71491,7 +71483,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>381</v>
@@ -71608,7 +71600,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>385</v>
@@ -71725,7 +71717,7 @@
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>390</v>
@@ -71842,7 +71834,7 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>396</v>
@@ -71961,7 +71953,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>404</v>
@@ -72080,7 +72072,7 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>412</v>
@@ -72109,10 +72101,10 @@
         <v>195</v>
       </c>
       <c r="L581" t="s" s="2">
+        <v>1061</v>
+      </c>
+      <c r="M581" t="s" s="2">
         <v>1062</v>
-      </c>
-      <c r="M581" t="s" s="2">
-        <v>1063</v>
       </c>
       <c r="N581" t="s" s="2">
         <v>415</v>
@@ -72197,7 +72189,7 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>419</v>
@@ -72316,7 +72308,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>427</v>

--- a/StructureDefinition-access-data-reporting-composition.xlsx
+++ b/StructureDefinition-access-data-reporting-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-data-reporting-composition.xlsx
+++ b/StructureDefinition-access-data-reporting-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1082,7 +1082,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|2018-08-12</t>
   </si>
   <si>
     <t>DocumentReference.event.code</t>

--- a/StructureDefinition-access-data-reporting-composition.xlsx
+++ b/StructureDefinition-access-data-reporting-composition.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-data-reporting-composition.xlsx
+++ b/StructureDefinition-access-data-reporting-composition.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
